--- a/接口测试用例Excel.xlsx
+++ b/接口测试用例Excel.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\postman-api-test-demo\testcase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36A23A9-E9E8-4596-8E2C-62E8DAAD4CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10310" yWindow="610" windowWidth="17370" windowHeight="13790" xr2:uid="{A6C672D9-2FBE-4A3A-9F71-7A9E68155671}"/>
+    <workbookView windowWidth="15540" windowHeight="12020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="71">
   <si>
     <t>用例 ID</t>
   </si>
@@ -57,36 +55,57 @@
     <t>测试类型</t>
   </si>
   <si>
+    <t>设计方法</t>
+  </si>
+  <si>
+    <t>风险点</t>
+  </si>
+  <si>
+    <t>实际结果</t>
+  </si>
+  <si>
     <t>TC001</t>
   </si>
   <si>
+    <t>查询单个用户</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>id=2</t>
+  </si>
+  <si>
+    <t>返回 id=2 用户信息</t>
+  </si>
+  <si>
+    <t>正向场景</t>
+  </si>
+  <si>
+    <t>等价类（有效等价）</t>
+  </si>
+  <si>
+    <t>正常查询，核心功能，改动容易出问题</t>
+  </si>
+  <si>
     <t>TC002</t>
   </si>
   <si>
-    <t>查询单个用户</t>
-  </si>
-  <si>
-    <t>GET</t>
-  </si>
-  <si>
-    <t>id=2</t>
-  </si>
-  <si>
     <t>id=9999</t>
   </si>
   <si>
-    <t>返回 id=2 用户信息</t>
-  </si>
-  <si>
     <t>无用户数据</t>
   </si>
   <si>
-    <t>正向场景</t>
-  </si>
-  <si>
     <t>异常场景</t>
   </si>
   <si>
+    <t>等价类（无效等价）</t>
+  </si>
+  <si>
+    <t>非法 id 如果返回脏数据，会误导前端</t>
+  </si>
+  <si>
     <t>TC003</t>
   </si>
   <si>
@@ -99,143 +118,500 @@
     <t>返回第 1 页用户列表数据，data 数组包含多条用户信息</t>
   </si>
   <si>
-    <t>设计方法</t>
-  </si>
-  <si>
-    <t>风险点</t>
-  </si>
-  <si>
-    <t>等价类（有效等价）</t>
-  </si>
-  <si>
-    <t>等价类（无效等价）</t>
+    <t>分页是前端核心渲染依赖，分页出错会导致页面展示异常</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>page=999</t>
+  </si>
+  <si>
+    <t>data 为空数组，无用户数据</t>
+  </si>
+  <si>
+    <t>边界场景</t>
   </si>
   <si>
     <t>边界值分析</t>
   </si>
   <si>
-    <t>正常查询，核心功能，改动容易出问题</t>
-  </si>
-  <si>
-    <t>非法 id 如果返回脏数据，会误导前端</t>
-  </si>
-  <si>
-    <t>分页是前端核心渲染依赖，分页出错会导致页面展示异常</t>
-  </si>
-  <si>
-    <t>TC004</t>
-  </si>
-  <si>
-    <t>page=999</t>
-  </si>
-  <si>
-    <t>data 为空数组，无用户数据</t>
-  </si>
-  <si>
-    <t>边界场景</t>
-  </si>
-  <si>
     <t>超大页码若报错，会造成前端页面崩溃</t>
   </si>
   <si>
     <t>TC005</t>
   </si>
   <si>
+    <t>创建用户</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>name:Lily, job:tester</t>
+  </si>
+  <si>
+    <t>返回用户信息，包含自动生成 id、创建时间</t>
+  </si>
+  <si>
+    <t>新增是核心写接口，校验失败会产生脏数据</t>
+  </si>
+  <si>
     <t>TC006</t>
   </si>
   <si>
+    <t>仅传入 job，不传 name</t>
+  </si>
+  <si>
+    <t>接口仍然返回 201，成功创建用户，没有拦截缺失 name 的请求</t>
+  </si>
+  <si>
+    <t>等价类（无效等价）+ 错误推测</t>
+  </si>
+  <si>
+    <t>缺少必填字段没有拦截，会产生缺少核心信息的脏数据</t>
+  </si>
+  <si>
     <t>TC007</t>
   </si>
   <si>
+    <t>更新用户信息</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>id=2，name:Lily, job:test-engineer</t>
+  </si>
+  <si>
+    <t>返回更新后的用户信息</t>
+  </si>
+  <si>
+    <t>用户信息是前端展示核心，更新错误会展示错误数据</t>
+  </si>
+  <si>
     <t>TC008</t>
   </si>
   <si>
-    <t>创建用户</t>
-  </si>
-  <si>
-    <t>POST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name:Lily, job:tester</t>
-  </si>
-  <si>
-    <t>返回用户信息，包含自动生成 id、创建时间</t>
-  </si>
-  <si>
-    <t>新增是核心写接口，校验失败会产生脏数据</t>
-  </si>
-  <si>
-    <t>仅传入 job，不传 name</t>
-  </si>
-  <si>
-    <t>接口仍然返回 201，成功创建用户，没有拦截缺失 name 的请求</t>
-  </si>
-  <si>
-    <t>等价类（无效等价）+ 错误推测</t>
-  </si>
-  <si>
-    <t>缺少必填字段没有拦截，会产生缺少核心信息的脏数据</t>
-  </si>
-  <si>
-    <t>更新用户信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PUT</t>
-  </si>
-  <si>
-    <t>id=2，name:Lily, job:test-engineer</t>
-  </si>
-  <si>
-    <t>返回更新后的用户信息</t>
-  </si>
-  <si>
-    <t>用户信息是前端展示核心，更新错误会展示错误数据</t>
-  </si>
-  <si>
     <t>id=9999，传入 name 和 job</t>
   </si>
   <si>
+    <t>id 不存在时接口依然返回 200，没有拦截，假装更新成功</t>
+  </si>
+  <si>
     <t>等价类（无效等价）+ 边界值</t>
   </si>
   <si>
-    <t>id 不存在时接口依然返回 200，没有拦截，假装更新成功</t>
-  </si>
-  <si>
     <t>更新不存在 id 会造成数据错乱，容易误导前端以为修改成功</t>
+  </si>
+  <si>
+    <t>TC009</t>
+  </si>
+  <si>
+    <t>创建用户，Body 为空 {}</t>
+  </si>
+  <si>
+    <t>/users，body {}</t>
+  </si>
+  <si>
+    <t>校验 body 不能为空，返回参数错误，不创建用户</t>
+  </si>
+  <si>
+    <t>无效等价类</t>
+  </si>
+  <si>
+    <t>失败</t>
+  </si>
+  <si>
+    <t>TC012</t>
+  </si>
+  <si>
+    <t>PUT 更新用户，路径 id 传字符串 abc123</t>
+  </si>
+  <si>
+    <t>/users/abc123</t>
+  </si>
+  <si>
+    <t>校验 id 格式，返回参数非法</t>
+  </si>
+  <si>
+    <t>S01</t>
+  </si>
+  <si>
+    <t>创建用户→动态提取 ID→查询→更新完整链路</t>
+  </si>
+  <si>
+    <t>创建成功，可查询新建用户，更新生效，链路通畅</t>
+  </si>
+  <si>
+    <t>GET 返回 404，失败</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -243,9 +619,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -254,23 +872,67 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -319,7 +981,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -352,26 +1014,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -404,23 +1049,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -562,28 +1190,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563B014B-67F1-4C86-922F-D894B2E44CC0}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="5" max="5" width="11.58203125" customWidth="1"/>
-    <col min="6" max="6" width="17.08203125" customWidth="1"/>
-    <col min="8" max="8" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.75" customWidth="1"/>
+    <col min="5" max="5" width="11.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="18.25" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -606,113 +1229,116 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
         <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2">
+        <v>404</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1">
-        <v>404</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="E4" s="2">
+        <v>200</v>
+      </c>
+      <c r="F4" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1">
-        <v>200</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>200</v>
       </c>
       <c r="F5" t="s">
@@ -722,73 +1348,73 @@
         <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" s="2">
+        <v>201</v>
+      </c>
+      <c r="F6" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="1">
-        <v>201</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
         <v>42</v>
       </c>
+      <c r="E7" s="2">
+        <v>201</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="1">
-        <v>201</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" t="s">
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>47</v>
@@ -799,7 +1425,7 @@
       <c r="D8" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>200</v>
       </c>
       <c r="F8" t="s">
@@ -809,15 +1435,15 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
         <v>47</v>
@@ -826,26 +1452,101 @@
         <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="1">
+        <v>53</v>
+      </c>
+      <c r="E9" s="2">
         <v>200</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I9" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10">
+        <v>404</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13">
+        <v>404</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>